--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.85264177558727</v>
+        <v>7.613554288532932</v>
       </c>
       <c r="D2" t="n">
-        <v>46.2211976032322</v>
+        <v>7.510944610525232</v>
       </c>
       <c r="E2" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F2" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.79003801027371</v>
+        <v>2.078381176669478</v>
       </c>
       <c r="D3" t="n">
-        <v>12.7592607423065</v>
+        <v>2.073379870624807</v>
       </c>
       <c r="E3" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F3" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.32923101277174</v>
+        <v>5.578500039575409</v>
       </c>
       <c r="D4" t="n">
-        <v>34.27782262022524</v>
+        <v>5.570146175786602</v>
       </c>
       <c r="E4" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F4" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.38819590119964</v>
+        <v>3.800581833944941</v>
       </c>
       <c r="D5" t="n">
-        <v>23.24920943515514</v>
+        <v>3.77799653321271</v>
       </c>
       <c r="E5" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F5" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.78754742560108</v>
+        <v>5.165476456660175</v>
       </c>
       <c r="D6" t="n">
-        <v>30.98806488698131</v>
+        <v>5.035560544134463</v>
       </c>
       <c r="E6" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F6" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.86108387794484</v>
+        <v>6.639926130166037</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60670600790473</v>
+        <v>6.598589726284519</v>
       </c>
       <c r="E7" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F7" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.14860205025475</v>
+        <v>2.949147833166397</v>
       </c>
       <c r="D8" t="n">
-        <v>18.05276515358507</v>
+        <v>2.933574337457574</v>
       </c>
       <c r="E8" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F8" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.9467693895189</v>
+        <v>4.216350025796821</v>
       </c>
       <c r="D9" t="n">
-        <v>26.71469550691425</v>
+        <v>4.341138019873566</v>
       </c>
       <c r="E9" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F9" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.32482823216078</v>
+        <v>5.577784587726127</v>
       </c>
       <c r="D10" t="n">
-        <v>34.06145182662448</v>
+        <v>5.534985921826478</v>
       </c>
       <c r="E10" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F10" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.27197384273773</v>
+        <v>7.031695749444881</v>
       </c>
       <c r="D11" t="n">
-        <v>43.68493049862905</v>
+        <v>7.098801206027221</v>
       </c>
       <c r="E11" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F11" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>3.650022654339454</v>
+        <v>0.5931286813301613</v>
       </c>
       <c r="D12" t="n">
-        <v>3.855536004869691</v>
+        <v>0.6265246007913248</v>
       </c>
       <c r="E12" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F12" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.52858712910901</v>
+        <v>7.398395408480215</v>
       </c>
       <c r="D13" t="n">
-        <v>46.1129204253498</v>
+        <v>7.493349569119342</v>
       </c>
       <c r="E13" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F13" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.18973207110773</v>
+        <v>4.580831461555006</v>
       </c>
       <c r="D14" t="n">
-        <v>27.31184700700092</v>
+        <v>4.43817513863765</v>
       </c>
       <c r="E14" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F14" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.08395882508369</v>
+        <v>6.5136433090761</v>
       </c>
       <c r="D15" t="n">
-        <v>40.49552881012695</v>
+        <v>6.58052343164563</v>
       </c>
       <c r="E15" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F15" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.91066118938209</v>
+        <v>6.64798244327459</v>
       </c>
       <c r="D16" t="n">
-        <v>41.15117416864437</v>
+        <v>6.687065802404711</v>
       </c>
       <c r="E16" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F16" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>56.29139727874001</v>
+        <v>9.147352057795251</v>
       </c>
       <c r="D17" t="n">
-        <v>56.45282564884153</v>
+        <v>9.173584167936749</v>
       </c>
       <c r="E17" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F17" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.58466889931496</v>
+        <v>7.732508696138682</v>
       </c>
       <c r="D18" t="n">
-        <v>46.63942515541378</v>
+        <v>7.578906587754739</v>
       </c>
       <c r="E18" t="n">
-        <v>13.36144114347071</v>
+        <v>2.171234185813991</v>
       </c>
       <c r="F18" t="n">
-        <v>13.34113709867449</v>
+        <v>2.167934778534605</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
